--- a/output/pdf_financials_xlsx/EVNI.xlsx
+++ b/output/pdf_financials_xlsx/EVNI.xlsx
@@ -2482,13 +2482,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.435634</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.676624</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.874021</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
@@ -4767,7 +4767,11 @@
           <t>Warrants reserve 8</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>0.435634</v>
       </c>
@@ -8873,10 +8877,10 @@
         </is>
       </c>
       <c r="H133" s="5" t="n">
-        <v>2.792647</v>
+        <v>-2.792647</v>
       </c>
       <c r="I133" s="5" t="n">
-        <v>3.153199</v>
+        <v>-3.153199</v>
       </c>
     </row>
     <row r="134">
@@ -10008,10 +10012,10 @@
         </is>
       </c>
       <c r="G161" s="5" t="n">
-        <v>4.14952</v>
+        <v>-4.14952</v>
       </c>
       <c r="H161" s="5" t="n">
-        <v>2.792647</v>
+        <v>-2.792647</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/EVNI.xlsx
+++ b/output/pdf_financials_xlsx/EVNI.xlsx
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>2.973762</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>5.232955</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-2.973762</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-5.00156</v>
@@ -672,16 +672,16 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00495</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.020692</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.110201</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.156984</v>
       </c>
     </row>
     <row r="13">
@@ -1022,16 +1022,16 @@
         <v>-2.973762</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.232955</v>
+        <v>-5.237905</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.14952</v>
+        <v>-4.170212</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.792647</v>
+        <v>-2.902848</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.792647</v>
+        <v>-2.949631</v>
       </c>
     </row>
     <row r="28">
@@ -1066,16 +1066,16 @@
         <v>-2.973411</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.219283</v>
+        <v>-5.224233</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.121654</v>
+        <v>-4.142346</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.768679</v>
+        <v>-2.87888</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.776068</v>
+        <v>-2.933052</v>
       </c>
     </row>
     <row r="30">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.374506</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.529742</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.142748</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.985699</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.345092</v>
       </c>
     </row>
     <row r="35">
@@ -1222,19 +1222,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.374506</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.529742</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.142748</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>5.128172</v>
+        <v>6.113871</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1.930866</v>
+        <v>2.275958</v>
       </c>
     </row>
     <row r="37">
@@ -1486,19 +1486,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.649198</v>
+        <v>0.274692</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.104835</v>
+        <v>0.575093</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.408413</v>
+        <v>0.265665</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.354343</v>
+        <v>0.368644</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.7313539999999999</v>
+        <v>0.386262</v>
       </c>
     </row>
     <row r="49">
@@ -3184,13 +3184,13 @@
         <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.001427</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.04104</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.003629</v>
       </c>
       <c r="F124" s="3" t="n">
         <v>0</v>
@@ -3206,13 +3206,13 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.001427</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.04104</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.003629</v>
       </c>
       <c r="F125" s="3" t="n">
         <v>0</v>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
@@ -6323,7 +6323,11 @@
           <t>Lease payments 6</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -8657,7 +8661,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -9877,7 +9881,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10896,7 +10900,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -12079,7 +12083,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -12165,7 +12169,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E214" s="5" t="n">

--- a/output/pdf_financials_xlsx/EVNI.xlsx
+++ b/output/pdf_financials_xlsx/EVNI.xlsx
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.012963</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>-0.068855</v>
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.07027899999999999</v>
+        <v>-0.083242</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>1.243906</v>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.025241</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.02495</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.025241</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.02495</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -7554,7 +7554,11 @@
           <t>Purchase of equipment 5</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -8128,7 +8132,11 @@
           <t>HST recoverable</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E115" s="5" t="n">
         <v>-0.012963</v>
       </c>
@@ -8290,7 +8298,11 @@
           <t>Purchase of equipment 5</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E119" s="5" t="n">
         <v>-0.025241</v>
       </c>
